--- a/crm/v2/lgo/integral-top200-pharmaland.xlsx
+++ b/crm/v2/lgo/integral-top200-pharmaland.xlsx
@@ -434,7 +434,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -451,7 +451,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>PRIX REMISE HT</t>
+          <t>PRIX NET HT</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">

--- a/crm/v2/lgo/integral-top200-pharmaland.xlsx
+++ b/crm/v2/lgo/integral-top200-pharmaland.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catalogue'!$A$1:$D$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catalogue'!$A$1:$J$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -57,13 +59,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,2775 +432,5551 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:J201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>CODE ARTICLE</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>CIP13</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>GAMME</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>(fixe)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>(fixe)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>(fixe)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LIBELLE</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>PRIX NET HT</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>GAMME</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TVA</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ABANDON DE MARGE</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>3474419</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>3400934744198</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>KARDEGIC 75MG PDR SACH 30</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="H2" s="3" t="n">
         <v>1.29</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I2" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>4960553</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>3400949605538</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>IZALGI 500MG/25MG GELU BT16</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I3" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>3200509</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>3400932005093</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>DIPROSTENE INJ SERING1ML 1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="H4" s="3" t="n">
         <v>3.71</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I4" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>6223413</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>3662042005664</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>THEALOSE SOL OPHT FL 15ML T</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>8.34</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I5" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>3324737</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>3400933247379</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>KARDEGIC 160MG PDR SACH 30</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>1.29</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I6" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>3515495</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>3400935154958</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>LAMALINE GELU BT16</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="H7" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I7" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>3098608</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>3400930986080</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>SPASFON CPR BT30</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="H8" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I8" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>3029291</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>3400930292914</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>MOUNJARO 5MG INJ STYLO KWIKPEN 1</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>212.71</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H9" s="3" t="n">
+        <v>212.74</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>2238562</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>3400922385624</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>HELICIDINE 10% S/S SIR FP250ML</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>2.34</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I10" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>3290599</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>3400932905997</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>DIFFU-K 600MG GELU BT40</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="H11" s="3" t="n">
         <v>1.61</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I11" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>3029290</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>3400930292907</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>MOUNJARO 2,5MG INJ STYLO KWIKPEN 1</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>157.33</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H12" s="3" t="n">
+        <v>157.36</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>3443873</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>3400934438738</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>VENTOLINE 100MCG INH FL200DOS 1</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I13" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>6042767</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>4028694001468</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>VISMED MULTI GTT LUBR FL15ML T</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="H14" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I14" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>4066958</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>3401040669580</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>HYLO CONFORT+COLLY HYD F10ML T</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="H15" s="3" t="n">
         <v>7.02</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I15" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>3216290</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>3400932162901</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>SKIACOL 0,5% COLLY FL0,5ML</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="H16" s="3" t="n">
         <v>7.11</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I16" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>3005620</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>3400930056202</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>GARDASIL 9 INJ SRG0,5ML 1+2AIG</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>103.38</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H17" s="3" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>3138414</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>3400931384144</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>STERDEX POM OPHT UNIDOS 12</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="H18" s="3" t="n">
         <v>1.73</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I18" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>3130737</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>3400931307372</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>NORMACOL LAVEMENT AD. D.130ML</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="H19" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I19" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>3552898</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>3400935528988</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>IBUFETUM 5% GEL TB60G</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="H20" s="3" t="n">
         <v>1.61</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I20" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>2686303</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>3400926863036</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>BEXSERO INJ SRG0,5ML 1 +AIG</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>70.48999999999999</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H21" s="3" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>3267672</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>3400932676729</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>ANTADYS 100MG CPR BT15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="H22" s="3" t="n">
         <v>2.04</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I22" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>3034844</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>3400930348444</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>EDUCTYL AD. SUP EFFV BT12</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="H23" s="3" t="n">
         <v>1.29</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I23" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>3186301</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>3400931863014</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>SPASFON LYOC 80MG LYOT ORAL 10</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="H24" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I24" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>3019275</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>3400930192757</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>SLINDA 4MG CPR PELLIC BT28X3</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="H25" s="3" t="n">
         <v>26.16</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I25" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>3309525</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>3400933095253</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>GAVISCON BUV SUSP SACH10ML 24</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="H26" s="3" t="n">
         <v>3.42</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I26" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>3171050</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>3400931710509</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>VIT B12 DEL.1000MCG INJ A.2ML 6</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="H27" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I27" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>3535836</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>3400935358363</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>ZYMAD 10000UI/ML BUV GTT 10ML</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="H28" s="3" t="n">
         <v>1.53</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I28" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>3479670</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>3400934796708</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>DACUDOSES OPHT UNIDOS10ML 24</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="H29" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I29" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>3234017</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>3400932340170</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>FLUVERMAL CPR BT6</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="H30" s="3" t="n">
         <v>2.02</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I30" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>3014186</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>3400930141861</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>SHINGRIX INJ FL+FL 1</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>168.37</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H31" s="3" t="n">
+        <v>168.39</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>3006555</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>3400930065556</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>LEVOTHYROX 25MCG CPR BT30 EXC</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="H32" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I32" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>3030312</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>3400930303122</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>EYLEA 114,3MG/ML INJ SRG 1</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>351.98</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H33" s="3" t="n">
+        <v>352.02</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>3006578</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>3400930065785</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>LEVOTHYROX 75MCG CPR BT30 EXC</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I34" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>3625137</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>3400936251373</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>SPIFEN 400MG CPR BT20</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="H35" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I35" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>3002858</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>3400930028582</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>REPATHA 140MG INJ STYLO1ML 1</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v>164.42</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H36" s="3" t="n">
+        <v>164.44</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>3778421</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>3400937784214</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>FLECTOR 1% GEL FL100G</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="H37" s="3" t="n">
         <v>2.24</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I37" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>6006071</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>3401060060718</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>OPTIVE  FUSION COLLYRE FL 10 ML</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="H38" s="3" t="n">
         <v>5.61</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I38" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>2673826</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>3400926738266</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>MONOPROST 50MCG/ML COLLY DOS30</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H39" s="3" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>3461546</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>3400934615467</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>DOLIPRANE 2,4% BUV FV100ML 1</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="H40" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I40" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>2225720</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>3400922257204</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>ELUDRILPERIO BAIN BCHE FL200ML</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="H41" s="3" t="n">
         <v>2.02</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I41" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>3006566</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>3400930065662</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>LEVOTHYROX 50MCG CPR BT30 EXC</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="H42" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I42" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>3325406</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>3400933254063</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>METEOSPASMYL CAPS BT20</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="H43" s="3" t="n">
         <v>2.18</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I43" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>3006589</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>3400930065891</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>LEVOTHYROX 100MCG CPR BT30 EXC</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="H44" s="3" t="n">
         <v>1.59</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I44" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>9000008</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>3664490000086</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>NEOVIS TOT MULTI GTT FL15ML T</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="H45" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I45" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>3244079</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>3400932440795</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>FLUVERMAL 2% BUV FL30ML</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="H46" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I46" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>6223558</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>4028694001413</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>VISMED GEL MULTI GTT LUBR FL15ML (NEW)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="H47" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I47" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>3029293</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>3400930292938</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>MOUNJARO 7,5MG INJ STYLO KWIKPEN 1</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n">
-        <v>301.08</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H48" s="3" t="n">
+        <v>301.11</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>3192750</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>3400931927501</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>STAGID 700MG CPR BT30</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="H49" s="3" t="n">
         <v>1.76</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I49" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>3535606</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>3400935356062</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>DERINOX SOL NAS FL15ML +POMP</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H50" s="3" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>3024437</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>3400930244371</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>VAXNEUVANCE</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n">
-        <v>43.36</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H51" s="3" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>3293534</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>3400932935345</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>CLARADOL 500MG CAFEINE CPR 16</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="H52" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I52" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>3464668</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>3400934646683</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>INDOCOLLYRE 0,1% COLLY DOS 20</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="H53" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I53" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>3066933</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>3400930669334</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>METEOXANE GELU BT60</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="H54" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I54" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>3687374</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>3400936873742</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>REPEVAX INJ SRG 1 S/A+1</t>
         </is>
       </c>
-      <c r="C55" s="3" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H55" s="3" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>3820382</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>3400938203820</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>AZYTER COLLY UNIDOS 6</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="H56" s="3" t="n">
         <v>4.12</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I56" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>3351800</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>3400933518004</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>TARDYFERON 80MG CPR BT30</t>
         </is>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="H57" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I57" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>2225393</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>3400922253930</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>NIMENRIX INJ FL+SRG 1 A/2AIG</t>
         </is>
       </c>
-      <c r="C58" s="3" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H58" s="3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>3000376</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>3400930003763</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>TRULICITY 1,5MG INJ STY0,5ML 4</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n">
-        <v>71.39</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H59" s="3" t="n">
+        <v>71.42</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>3015110</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>3400930151105</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>OZEMPIC 1MG INJ STYLO3ML 1</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n">
-        <v>68.23</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H60" s="3" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>3012140</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>3400930121405</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>LEVOTHYROX 75MCG CPR BT90 EXC</t>
         </is>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="H61" s="3" t="n">
         <v>3.45</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I61" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>3218969</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>3400932189694</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>LOCOID 0,1% CR TB30G</t>
         </is>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="H62" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I62" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>3595583</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>3400935955838</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>DOLIPRANE 1000MG CPR BT8</t>
         </is>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="H63" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I63" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>3113638</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>3400931136385</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>VIT B12 GERDA 1000MCG AMP4ML 6</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="H64" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I64" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>3189363</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>3400931893639</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>ASPEGIC BB. 100MG BUV SACH 20</t>
         </is>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="H65" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I65" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>3025862</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>3400930258620</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>WEGOVY 0,25MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n">
-        <v>131.19</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H66" s="3" t="n">
+        <v>131.21</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>3192253</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>3400931922537</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>PANOTILE GTT AURIC FL8ML</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="H67" s="3" t="n">
         <v>1.42</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I67" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>3006568</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>3400930065686</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>LEVOTHYROX 50MCG CPR BT90 EXC</t>
         </is>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="H68" s="3" t="n">
         <v>2.31</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I68" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>3023000</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>3400930230008</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>ASPIRINE PROTECT 100MG CPR 30</t>
         </is>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="H69" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I69" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>3233153</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>3400932331536</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>DOLIPRANE 500MG PDR SACH 12</t>
         </is>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="H70" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I70" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>3174284</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>3400931742845</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>LEXOMIL 6MG CPR TB30</t>
         </is>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="H71" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I71" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>6311785</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>3614790000712</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>ELIXYA SOL OPHT HYD FL 10ML T</t>
         </is>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="H72" s="3" t="n">
         <v>6.21</v>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I72" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>3006601</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>3400930066010</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>LEVOTHYROX 125MCG CPR BT30 EXC</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="H73" s="3" t="n">
         <v>1.95</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I73" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>3707125</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>3400937071253</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>RHINOMAXIL 100MCG NAS PULV120D.</t>
         </is>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="H74" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I74" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>3158575</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>3400931585756</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>TRIDESONIT 0,05% CR TB30G</t>
         </is>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="H75" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I75" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>3041867</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>3400930418673</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>FUNGIZONE 10% BUV FL40ML</t>
         </is>
       </c>
-      <c r="C76" s="3" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H76" s="3" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>4153396</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>3400941533969</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>DOLIPRANE 1000MG GELU BT8</t>
         </is>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="H77" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I77" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>3624698</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>3400936246980</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>DOLIPRANE 1000MG BUV SACH 8</t>
         </is>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="H78" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I78" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>3026454</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>3400930264546</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>COUMADINE 2MG CPR BT20</t>
         </is>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="H79" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I79" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>3025866</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>3400930258668</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>WEGOVY 2,4MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
-      <c r="C80" s="3" t="n">
-        <v>174.42</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>174.45</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>4168624</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>3400941686245</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>SPASFON LYOC 160MG LYOT ORAL 5</t>
         </is>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="H81" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I81" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>3025864</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>3400930258644</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>WEGOVY 1MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
-      <c r="C82" s="3" t="n">
-        <v>131.19</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H82" s="3" t="n">
+        <v>131.21</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>3513734</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>3400935137340</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>PRIORIX INJ FL+SRG 1 +2AIG</t>
         </is>
       </c>
-      <c r="C83" s="3" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H83" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>3391308</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>3400933913083</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>ESTREVA GEL FL-DOS 50G</t>
         </is>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="H84" s="3" t="n">
         <v>4.46</v>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I84" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>3747768</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>3400937477680</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>DEXAFREE 1MG/ML COLLY DOS 30</t>
         </is>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="H85" s="3" t="n">
         <v>3.69</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I85" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>3279066</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>3400932790661</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>OTIPAX SOL INSTIL AUR FV16G+CG</t>
         </is>
       </c>
-      <c r="C86" s="3" t="n">
+      <c r="H86" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I86" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>3021645</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>3400930216453</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>TRULICITY 3MG INJ STY0,5ML 4</t>
         </is>
       </c>
-      <c r="C87" s="3" t="n">
-        <v>71.39</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H87" s="3" t="n">
+        <v>71.42</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>3029294</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>3400930292945</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>MOUNJARO 10MG INJ STYLO KWIKPEN 1</t>
         </is>
       </c>
-      <c r="C88" s="3" t="n">
-        <v>301.08</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H88" s="3" t="n">
+        <v>301.11</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>3135858</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>3400931358589</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>PYOSTACINE 500MG CPR BT16</t>
         </is>
       </c>
-      <c r="C89" s="3" t="n">
+      <c r="H89" s="3" t="n">
         <v>15.92</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I89" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>3264550</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>3400932645503</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>TOCO 500MG CAPS MOL BT30</t>
         </is>
       </c>
-      <c r="C90" s="3" t="n">
+      <c r="H90" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I90" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>3023497</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>3400930234976</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>UVEDOSE 50000UI CAPS MOL BT2</t>
         </is>
       </c>
-      <c r="C91" s="3" t="n">
+      <c r="H91" s="3" t="n">
         <v>1.78</v>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I91" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>3499945</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>3400934999451</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>DOLIPRANE 300MG PDR SACH 12</t>
         </is>
       </c>
-      <c r="C92" s="3" t="n">
+      <c r="H92" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I92" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>3105283</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>3400931052838</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>THERALENE 5MG CPR PELLIC BT50</t>
         </is>
       </c>
-      <c r="C93" s="3" t="n">
+      <c r="H93" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I93" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>3118794</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>3400931187943</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>FEROGRAD VIT C 500 CPR BT30</t>
         </is>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="H94" s="3" t="n">
         <v>1.92</v>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I94" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>3006557</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>3400930065570</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>LEVOTHYROX 25MCG CPR BT90 EXC</t>
         </is>
       </c>
-      <c r="C95" s="3" t="n">
+      <c r="H95" s="3" t="n">
         <v>1.26</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I95" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>3228577</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>3400932285778</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>STRESAM GELU BT60</t>
         </is>
       </c>
-      <c r="C96" s="3" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H96" s="3" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>4066912</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>3401040669122</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>HYLO CONFORT COLLY HYD F10ML T</t>
         </is>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="H97" s="3" t="n">
         <v>7.02</v>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I97" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>3008456</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>3400930084564</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>ATURGYL 0,05% NAS FL15ML</t>
         </is>
       </c>
-      <c r="C98" s="3" t="n">
+      <c r="H98" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I98" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>2217904</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>3400922179049</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>OPTILOVA 20MCG/100MCG CPR 28X3</t>
         </is>
       </c>
-      <c r="C99" s="3" t="n">
+      <c r="H99" s="3" t="n">
         <v>3.23</v>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I99" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>3020488</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>3400930204887</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>KLIPAL 600MG/50MG CPR BT12</t>
         </is>
       </c>
-      <c r="C100" s="3" t="n">
+      <c r="H100" s="3" t="n">
         <v>1.38</v>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I100" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>3021648</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>3400930216484</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>TRULICITY 4,5MG INJ STY0,5ML 4</t>
         </is>
       </c>
-      <c r="C101" s="3" t="n">
-        <v>71.39</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H101" s="3" t="n">
+        <v>71.42</v>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>3570614</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>3400935706140</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>TIMOFEROL GELU BT30</t>
         </is>
       </c>
-      <c r="C102" s="3" t="n">
+      <c r="H102" s="3" t="n">
         <v>1.42</v>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I102" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>3026024</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>3400930260241</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>WEGOVY 1,7MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
-      <c r="C103" s="3" t="n">
-        <v>151.25</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H103" s="3" t="n">
+        <v>151.27</v>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>3529422</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>3400935294227</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>DOLIPRANE 1000MG CPR EFFV TB8</t>
         </is>
       </c>
-      <c r="C104" s="3" t="n">
+      <c r="H104" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I104" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>3189819</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>3400931898191</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>ASPEGIC AD. 1000MG BUV SACH 20</t>
         </is>
       </c>
-      <c r="C105" s="3" t="n">
+      <c r="H105" s="3" t="n">
         <v>2.23</v>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I105" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>3192767</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>3400931927679</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr">
         <is>
           <t>STAGID 700MG CPR BT100</t>
         </is>
       </c>
-      <c r="C106" s="3" t="n">
+      <c r="H106" s="3" t="n">
         <v>4.92</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I106" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>3348413</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>3400933484132</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr">
         <is>
           <t>PREVISCAN 20MG CPR BT30</t>
         </is>
       </c>
-      <c r="C107" s="3" t="n">
+      <c r="H107" s="3" t="n">
         <v>1.76</v>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I107" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>3422397</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>3400934223976</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>XYLOCAINE 10MG/ML S/C FL20ML 1</t>
         </is>
       </c>
-      <c r="C108" s="3" t="n">
+      <c r="H108" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I108" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>2735007</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>3400927350078</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr">
         <is>
           <t>HEXYON INJ SRG0,5ML 1 + 1AIG</t>
         </is>
       </c>
-      <c r="C109" s="3" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H109" s="3" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="I109" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>3480940</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>3400934809408</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>DOLIPRANE 150MG SUP BT10</t>
         </is>
       </c>
-      <c r="C110" s="3" t="n">
+      <c r="H110" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I110" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>3230829</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>3400932308293</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr">
         <is>
           <t>DIPROSONE 0,05% POM TB30G</t>
         </is>
       </c>
-      <c r="C111" s="3" t="n">
+      <c r="H111" s="3" t="n">
         <v>2.41</v>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I111" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>3446417</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>3400934464171</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="inlineStr">
         <is>
           <t>PAROEX 0,12% BAIN BCHE F300ML</t>
         </is>
       </c>
-      <c r="C112" s="3" t="n">
+      <c r="H112" s="3" t="n">
         <v>2.02</v>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I112" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>3644146</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>3400936441460</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr">
         <is>
           <t>PLAQUENIL 200MG CPR PEL BT30</t>
         </is>
       </c>
-      <c r="C113" s="3" t="n">
+      <c r="H113" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I113" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>3153342</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>3400931533429</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>POLYDEXA SOL AURIC FL10,5ML</t>
         </is>
       </c>
-      <c r="C114" s="3" t="n">
+      <c r="H114" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I114" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>2669210</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>3400926692100</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="inlineStr">
         <is>
           <t>MELAXOSE PATE ORAL POT P150G+C</t>
         </is>
       </c>
-      <c r="C115" s="3" t="n">
+      <c r="H115" s="3" t="n">
         <v>3.42</v>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I115" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>3412594</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>3400934125942</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="inlineStr">
         <is>
           <t>GYDRELLE 0,1% CR VAG TB30G</t>
         </is>
       </c>
-      <c r="C116" s="3" t="n">
+      <c r="H116" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I116" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>3001667</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>3400930016671</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="inlineStr">
         <is>
           <t>TOUJEO 300U SOLOSTAR STY1,5ML3</t>
         </is>
       </c>
-      <c r="C117" s="3" t="n">
-        <v>31.05</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H117" s="3" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="I117" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>5437210</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>3401554372105</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>SYSTANE BAL GTT OCUL LUB10ML T</t>
         </is>
       </c>
-      <c r="C118" s="3" t="n">
+      <c r="H118" s="3" t="n">
         <v>8.52</v>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I118" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>3105308</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>3400931053088</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>THERALENE 4% BUV GTT FL30ML</t>
         </is>
       </c>
-      <c r="C119" s="3" t="n">
+      <c r="H119" s="3" t="n">
         <v>1.62</v>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I119" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>3140500</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>3400931405009</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr">
         <is>
           <t>LEPTICUR 10MG CPR BT30</t>
         </is>
       </c>
-      <c r="C120" s="3" t="n">
+      <c r="H120" s="3" t="n">
         <v>3.52</v>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I120" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>2788676</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>3400927886768</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr">
         <is>
           <t>XIGDUO 5MG/1000MG CPR BT60</t>
         </is>
       </c>
-      <c r="C121" s="3" t="n">
+      <c r="H121" s="3" t="n">
         <v>32.37</v>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I121" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>3419538</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>3400934195389</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
         <is>
           <t>INDOCOLLYRE 0,1% COLLY FL5ML</t>
         </is>
       </c>
-      <c r="C122" s="3" t="n">
+      <c r="H122" s="3" t="n">
         <v>2.59</v>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I122" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>3019529</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>3400930195291</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr">
         <is>
           <t>BAQSIMI 3MG PDR NAS UNIDOS  1</t>
         </is>
       </c>
-      <c r="C123" s="3" t="n">
+      <c r="H123" s="3" t="n">
         <v>52.41</v>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I123" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>3403589</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>3400934035890</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
         <is>
           <t>ARTELAC 1,6MG/0,5ML CY DOS 60</t>
         </is>
       </c>
-      <c r="C124" s="3" t="n">
+      <c r="H124" s="3" t="n">
         <v>4.81</v>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I124" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>2678410</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>3400926784102</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr">
         <is>
           <t>ELIQUIS 5MG CPR BT60</t>
         </is>
       </c>
-      <c r="C125" s="3" t="n">
+      <c r="H125" s="3" t="n">
         <v>52.41</v>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I125" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>3023498</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>3400930234983</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
         <is>
           <t>UVEDOSE 50000UI CAPS MOL BT4</t>
         </is>
       </c>
-      <c r="C126" s="3" t="n">
+      <c r="H126" s="3" t="n">
         <v>3.44</v>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I126" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>3026231</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>3400930262313</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr">
         <is>
           <t>VITABACT 0,05% CY FL GTT10ML 1</t>
         </is>
       </c>
-      <c r="C127" s="3" t="n">
+      <c r="H127" s="3" t="n">
         <v>3.91</v>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I127" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>3005328</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>3400930053287</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
         <is>
           <t>ANTIBIO-SYNALAR AURIC SOL 10ML</t>
         </is>
       </c>
-      <c r="C128" s="3" t="n">
+      <c r="H128" s="3" t="n">
         <v>1.63</v>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I128" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>3491240</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>3400934912405</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr">
         <is>
           <t>MONAZOL 2% CR TB15G</t>
         </is>
       </c>
-      <c r="C129" s="3" t="n">
+      <c r="H129" s="3" t="n">
         <v>2.24</v>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I129" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>3012142</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>3400930121429</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
         <is>
           <t>LEVOTHYROX 100MCG CPR BT90 EXC</t>
         </is>
       </c>
-      <c r="C130" s="3" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H130" s="3" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I130" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>3338461</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>3400933384616</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr">
         <is>
           <t>FLECTOR 1% GEL TB60G - NSFP</t>
         </is>
       </c>
-      <c r="C131" s="3" t="n">
+      <c r="H131" s="3" t="n">
         <v>1.69</v>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I131" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>3015793</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>3400930157930</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr">
         <is>
           <t>LEVOTHYROX 88MCG CPR BT30</t>
         </is>
       </c>
-      <c r="C132" s="3" t="n">
+      <c r="H132" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I132" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>3219294</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>3400932192946</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr">
         <is>
           <t>DUPHASTON 10MG CPR BT10</t>
         </is>
       </c>
-      <c r="C133" s="3" t="n">
+      <c r="H133" s="3" t="n">
         <v>2.31</v>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I133" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>3232018</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>3400932320189</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="inlineStr">
         <is>
           <t>DOLIPRANE 500MG CPR BT16</t>
         </is>
       </c>
-      <c r="C134" s="3" t="n">
+      <c r="H134" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I134" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>3003791</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>3400930037911</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
         <is>
           <t>ENTRESTO 49MG/51MG CPR BT56</t>
         </is>
       </c>
-      <c r="C135" s="3" t="n">
+      <c r="H135" s="3" t="n">
         <v>98.15000000000001</v>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I135" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>3442307</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>3400934423079</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr">
         <is>
           <t>ADRIGYL 10000UI/ML GTT FL10ML</t>
         </is>
       </c>
-      <c r="C136" s="3" t="n">
+      <c r="H136" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I136" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>3162329</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>3400931623298</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr">
         <is>
           <t>COLPOTROPHINE CAPS VAG BT20</t>
         </is>
       </c>
-      <c r="C137" s="3" t="n">
+      <c r="H137" s="3" t="n">
         <v>3.67</v>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I137" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J137" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>3003790</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>3400930037904</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr">
         <is>
           <t>ENTRESTO 24MG/26MG CPR BT28</t>
         </is>
       </c>
-      <c r="C138" s="3" t="n">
+      <c r="H138" s="3" t="n">
         <v>49.06</v>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I138" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -3206,1018 +5985,2038 @@
           <t>4028694001499</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>4028694001499</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr">
         <is>
           <t>HYLOVIS MULTI GTT FL15ML 1</t>
         </is>
       </c>
-      <c r="C139" s="3" t="n">
+      <c r="H139" s="3" t="n">
         <v>8.49</v>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I139" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>2685798</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>3400926857981</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="inlineStr">
         <is>
           <t>TRESIBA 200U/ML INJ STYL.3ML 3</t>
         </is>
       </c>
-      <c r="C140" s="3" t="n">
-        <v>49.81</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H140" s="3" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="I140" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>3024785</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>3400930247853</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr">
         <is>
           <t>PREVENAR 20 INJ SRG0,5ML+AIG 1</t>
         </is>
       </c>
-      <c r="C141" s="3" t="n">
-        <v>50.28</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H141" s="3" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="I141" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>3677387</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>3400936773875</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr">
         <is>
           <t>BOOSTRIXTETRA INJ SRG0,5ML+A 1</t>
         </is>
       </c>
-      <c r="C142" s="3" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H142" s="3" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="I142" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J142" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>3772298</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>3400937722988</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>LANTUS 100U/ML INJ SOLO3ML 5</t>
         </is>
       </c>
-      <c r="C143" s="3" t="n">
-        <v>32.28</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H143" s="3" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="I143" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>3450778</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>3400934507786</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" t="inlineStr">
         <is>
           <t>DOLIPRANE 500MG GELU BT16</t>
         </is>
       </c>
-      <c r="C144" s="3" t="n">
+      <c r="H144" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I144" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J144" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>3015849</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>3400930158494</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="inlineStr">
         <is>
           <t>COSTEC 20+5MG/ML COLLY FL10ML1</t>
         </is>
       </c>
-      <c r="C145" s="3" t="n">
+      <c r="H145" s="3" t="n">
         <v>12.13</v>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I145" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J145" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>3295510</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>3400932955107</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>LOXEN LP 50MG GELU BT60</t>
         </is>
       </c>
-      <c r="C146" s="3" t="n">
+      <c r="H146" s="3" t="n">
         <v>9.98</v>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I146" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J146" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>3480986</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>3400934809866</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>DOLIPRANE 200MG SUP BT10</t>
         </is>
       </c>
-      <c r="C147" s="3" t="n">
+      <c r="H147" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I147" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J147" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>3003792</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>3400930037928</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="inlineStr">
         <is>
           <t>ENTRESTO 97MG/103MG CPR BT56</t>
         </is>
       </c>
-      <c r="C148" s="3" t="n">
+      <c r="H148" s="3" t="n">
         <v>98.15000000000001</v>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I148" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J148" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>3031116</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>3400930311165</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr">
         <is>
           <t>COLCHICINE MYS 1MG CPR BT30</t>
         </is>
       </c>
-      <c r="C149" s="3" t="n">
+      <c r="H149" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I149" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J149" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>7800001</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>3664478000015</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="inlineStr">
         <is>
           <t>HYLO LIPID COLLYRE FL3ML1</t>
         </is>
       </c>
-      <c r="C150" s="3" t="n">
+      <c r="H150" s="3" t="n">
         <v>7.62</v>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I150" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J150" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>3057302</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>3400930573020</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="inlineStr">
         <is>
           <t>LAROXYL 25MG CPR BT60</t>
         </is>
       </c>
-      <c r="C151" s="3" t="n">
+      <c r="H151" s="3" t="n">
         <v>2.89</v>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I151" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J151" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>3006618</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>3400930066188</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>LEVOTHYROX 150MCG CPR BT30 EXC</t>
         </is>
       </c>
-      <c r="C152" s="3" t="n">
+      <c r="H152" s="3" t="n">
         <v>2.32</v>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I152" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>3207026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>3400932070268</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="inlineStr">
         <is>
           <t>FLAMMAZINE CR TB50G</t>
         </is>
       </c>
-      <c r="C153" s="3" t="n">
+      <c r="H153" s="3" t="n">
         <v>2.83</v>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I153" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J153" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>3015804</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>3400930158043</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>LEVOTHYROX 112MCG CPR BT30</t>
         </is>
       </c>
-      <c r="C154" s="3" t="n">
+      <c r="H154" s="3" t="n">
         <v>1.77</v>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I154" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>3641662</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>3400936416628</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>SEPTIVON 1,5% CUTA FL250ML</t>
         </is>
       </c>
-      <c r="C155" s="3" t="n">
+      <c r="H155" s="3" t="n">
         <v>1.72</v>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I155" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>3768902</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>3400937689021</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="inlineStr">
         <is>
           <t>LACRIFLUID 0,13% CY UNIDOS 60</t>
         </is>
       </c>
-      <c r="C156" s="3" t="n">
+      <c r="H156" s="3" t="n">
         <v>4.81</v>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I156" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J156" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>3039698</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>3400930396988</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="inlineStr">
         <is>
           <t>FERROSTRANE ENF/AD SIR F125ML1</t>
         </is>
       </c>
-      <c r="C157" s="3" t="n">
+      <c r="H157" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I157" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>3027121</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>3400930271216</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="inlineStr">
         <is>
           <t>DIPROSALIC LOT FL30ML</t>
         </is>
       </c>
-      <c r="C158" s="3" t="n">
+      <c r="H158" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I158" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J158" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>3025251</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>3400930252512</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="inlineStr">
         <is>
           <t>NEFOPAM PANP 30MG CPR PEL BT30</t>
         </is>
       </c>
-      <c r="C159" s="3" t="n">
+      <c r="H159" s="3" t="n">
         <v>8.84</v>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I159" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J159" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>3113644</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>3400931136446</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="inlineStr">
         <is>
           <t>VIT B12 GERDA 250MCG CPR FL24</t>
         </is>
       </c>
-      <c r="C160" s="3" t="n">
+      <c r="H160" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I160" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>2761996</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>3400927619960</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="inlineStr">
         <is>
           <t>RELVAR ELLIPTA 92/22MCG 30DOSX1</t>
         </is>
       </c>
-      <c r="C161" s="3" t="n">
+      <c r="H161" s="3" t="n">
         <v>25.05</v>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I161" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J161" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>3010861</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>3400930108611</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" t="inlineStr">
         <is>
           <t>BETADINE SCRUB SOL FP125ML</t>
         </is>
       </c>
-      <c r="C162" s="3" t="n">
+      <c r="H162" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I162" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J162" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>3480911</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>3400934809118</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="inlineStr">
         <is>
           <t>DOLIPRANE 100MG SUP BT10</t>
         </is>
       </c>
-      <c r="C163" s="3" t="n">
+      <c r="H163" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I163" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J163" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>3014595</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>3400930145951</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="inlineStr">
         <is>
           <t>LEVOFREE 0,05% COLLY FL5ML 1</t>
         </is>
       </c>
-      <c r="C164" s="3" t="n">
+      <c r="H164" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I164" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>3204654</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>3400932046546</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>CYTEAL SOL MOUSS FP250ML</t>
         </is>
       </c>
-      <c r="C165" s="3" t="n">
+      <c r="H165" s="3" t="n">
         <v>2.21</v>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I165" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J165" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>3024059</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>3400930240595</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="inlineStr">
         <is>
           <t>RYALTRIS 25MCG/600MCG/DOS F30ML1</t>
         </is>
       </c>
-      <c r="C166" s="3" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H166" s="3" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="I166" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J166" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>3339756</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>3400933397562</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" t="inlineStr">
         <is>
           <t>KEAL 1G SUSP BUV SACH5ML 30</t>
         </is>
       </c>
-      <c r="C167" s="3" t="n">
+      <c r="H167" s="3" t="n">
         <v>7.89</v>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I167" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J167" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>3027120</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>3400930271209</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" t="inlineStr">
         <is>
           <t>DIPROSONE 0,05% LOT FL30ML</t>
         </is>
       </c>
-      <c r="C168" s="3" t="n">
+      <c r="H168" s="3" t="n">
         <v>2.41</v>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I168" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J168" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>4925031</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>3400949250318</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" t="inlineStr">
         <is>
           <t>ZALERG 0,25MG/ML COLLY FL5ML</t>
         </is>
       </c>
-      <c r="C169" s="3" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H169" s="3" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="I169" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J169" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>3025863</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>3400930258637</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="inlineStr">
         <is>
           <t>WEGOVY 0,5MG FLEX INJ STYLO SC 1</t>
         </is>
       </c>
-      <c r="C170" s="3" t="n">
-        <v>131.19</v>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H170" s="3" t="n">
+        <v>131.21</v>
+      </c>
+      <c r="I170" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J170" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>4194567</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>3400941945670</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="inlineStr">
         <is>
           <t>ELIQUIS 2,5MG CPR BT60</t>
         </is>
       </c>
-      <c r="C171" s="3" t="n">
+      <c r="H171" s="3" t="n">
         <v>52.41</v>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I171" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J171" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>3007978</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>3400930079782</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="inlineStr">
         <is>
           <t>VAXELIS INJ SRG0,5ML 1 +1AIG</t>
         </is>
       </c>
-      <c r="C172" s="3" t="n">
-        <v>28.35</v>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H172" s="3" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="I172" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J172" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>3149978</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>3400931499787</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" t="inlineStr">
         <is>
           <t>BETADINE 10% SOL LOC FL125ML</t>
         </is>
       </c>
-      <c r="C173" s="3" t="n">
+      <c r="H173" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I173" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J173" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
+          <t>3002411</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
           <t>3400930024119</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" t="inlineStr">
         <is>
           <t>SOOLANTRA 10MG/G CR TB30G 1</t>
         </is>
       </c>
-      <c r="C174" s="3" t="n">
+      <c r="H174" s="3" t="n">
         <v>25.82</v>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I174" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J174" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>2675268</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
           <t>3400926752682</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" t="inlineStr">
         <is>
           <t>OPTIDRIL 30MCG/150MCG CPR 28X3</t>
         </is>
       </c>
-      <c r="C175" s="3" t="n">
+      <c r="H175" s="3" t="n">
         <v>3.23</v>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I175" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J175" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
+          <t>3065253</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
           <t>3400930652534</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="inlineStr">
         <is>
           <t>MAXIDROL COLLY FL3ML</t>
         </is>
       </c>
-      <c r="C176" s="3" t="n">
+      <c r="H176" s="3" t="n">
         <v>1.48</v>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I176" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J176" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
+          <t>3588755</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
           <t>3400935887559</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="inlineStr">
         <is>
           <t>SERESTA 10MG CPR BT30</t>
         </is>
       </c>
-      <c r="C177" s="3" t="n">
+      <c r="H177" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I177" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J177" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
+          <t>3031324</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
           <t>3400930313244</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="inlineStr">
         <is>
           <t>ASARED 75MG CPR BT30</t>
         </is>
       </c>
-      <c r="C178" s="3" t="n">
+      <c r="H178" s="3" t="n">
         <v>1.36</v>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I178" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J178" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
+          <t>3004007</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
           <t>3400930040072</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="inlineStr">
         <is>
           <t>ABASAGLAR 100U STY(1-80U) 3ML5</t>
         </is>
       </c>
-      <c r="C179" s="3" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H179" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I179" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J179" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
+          <t>3516690</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>3400935166906</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" t="inlineStr">
         <is>
           <t>ENGERIX B 20MCG SRG.BACK.1ML 1</t>
         </is>
       </c>
-      <c r="C180" s="3" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H180" s="3" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="I180" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J180" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
+          <t>3263711</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
           <t>3400932637119</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" t="inlineStr">
         <is>
           <t>RHINOFLUIMUCIL NAS FL NEB 10ML</t>
         </is>
       </c>
-      <c r="C181" s="3" t="n">
+      <c r="H181" s="3" t="n">
         <v>4.66</v>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I181" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J181" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
+          <t>3032215</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
           <t>3400930322154</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="inlineStr">
         <is>
           <t>OZEMPIC 0,5MG INJ STYLO3ML 1</t>
         </is>
       </c>
-      <c r="C182" s="3" t="n">
-        <v>68.23</v>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="H182" s="3" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J182" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
+          <t>3248781</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
           <t>3400932487813</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="inlineStr">
         <is>
           <t>HAVLANE CPR BT20</t>
         </is>
       </c>
-      <c r="C183" s="3" t="n">
+      <c r="H183" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I183" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J183" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
+          <t>3442997</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
           <t>3400934429972</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="inlineStr">
         <is>
           <t>TOBRADEX COLLY FL5ML</t>
         </is>
       </c>
-      <c r="C184" s="3" t="n">
+      <c r="H184" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I184" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J184" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
+          <t>3301802</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
           <t>3400933018023</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" t="inlineStr">
         <is>
           <t>DEPAKINE CHRONO 500MG CPR TB30</t>
         </is>
       </c>
-      <c r="C185" s="3" t="n">
+      <c r="H185" s="3" t="n">
         <v>5.96</v>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I185" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
+          <t>3274850</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
           <t>3400932748501</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="inlineStr">
         <is>
           <t>AMYCOR 1% CR LOC TB15G</t>
         </is>
       </c>
-      <c r="C186" s="3" t="n">
+      <c r="H186" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I186" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J186" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
+          <t>3649793</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
           <t>3400936497931</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" t="inlineStr">
         <is>
           <t>VOGALENE 5MG SUP SECAB BT10</t>
         </is>
       </c>
-      <c r="C187" s="3" t="n">
+      <c r="H187" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I187" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J187" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
+          <t>3063219</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
           <t>3400930632192</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="inlineStr">
         <is>
           <t>LUMIRELAX 500MG CPR BT20</t>
         </is>
       </c>
-      <c r="C188" s="3" t="n">
+      <c r="H188" s="3" t="n">
         <v>7.42</v>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I188" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J188" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
+          <t>3707102</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
           <t>3400937071024</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="inlineStr">
         <is>
           <t>RINOCLENIL 100MCG NAS PULV120D.</t>
         </is>
       </c>
-      <c r="C189" s="3" t="n">
+      <c r="H189" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I189" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J189" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -4226,242 +8025,482 @@
           <t>3614790001054</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>3614790001054</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="inlineStr">
         <is>
           <t>NEREYA COLLY 0,24% FL10ML</t>
         </is>
       </c>
-      <c r="C190" s="3" t="n">
+      <c r="H190" s="3" t="n">
         <v>6.21</v>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I190" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J190" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
+          <t>3285552</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
           <t>3400932855520</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="inlineStr">
         <is>
           <t>EXACYL 500MG CPR PELLIC BT20</t>
         </is>
       </c>
-      <c r="C191" s="3" t="n">
+      <c r="H191" s="3" t="n">
         <v>2.34</v>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I191" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J191" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
+          <t>3278173</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
           <t>3400932781737</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" t="inlineStr">
         <is>
           <t>LOXEN 20MG CPR BT30</t>
         </is>
       </c>
-      <c r="C192" s="3" t="n">
+      <c r="H192" s="3" t="n">
         <v>3.21</v>
       </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I192" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J192" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
+          <t>3636684</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
           <t>3400936366848</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="inlineStr">
         <is>
           <t>MONOSEPT COLLY DOS 30</t>
         </is>
       </c>
-      <c r="C193" s="3" t="n">
+      <c r="H193" s="3" t="n">
         <v>2.46</v>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I193" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
+          <t>3239948</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
           <t>3400932399482</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="inlineStr">
         <is>
           <t>SURGAM 200MG CPR BT15</t>
         </is>
       </c>
-      <c r="C194" s="3" t="n">
+      <c r="H194" s="3" t="n">
         <v>1.69</v>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I194" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J194" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
+          <t>3481017</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
           <t>3400934810176</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="inlineStr">
         <is>
           <t>DOLIPRANE 300MG SUP BT10</t>
         </is>
       </c>
-      <c r="C195" s="3" t="n">
+      <c r="H195" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I195" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J195" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
+          <t>6025385</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
           <t>3662042003615</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="inlineStr">
         <is>
           <t>BLEPHACLEAN COMP STER PAUP 20</t>
         </is>
       </c>
-      <c r="C196" s="3" t="n">
+      <c r="H196" s="3" t="n">
         <v>8.93</v>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I196" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J196" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
+          <t>3222379</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
           <t>3400932223794</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" t="inlineStr">
         <is>
           <t>NERISONE CR TB30G</t>
         </is>
       </c>
-      <c r="C197" s="3" t="n">
+      <c r="H197" s="3" t="n">
         <v>1.93</v>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I197" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J197" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
+          <t>3413613</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
           <t>3400934136139</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="inlineStr">
         <is>
           <t>XOLAAM CPR CROQ BT40</t>
         </is>
       </c>
-      <c r="C198" s="3" t="n">
+      <c r="H198" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I198" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J198" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
+          <t>3691849</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
           <t>3400936918498</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="inlineStr">
         <is>
           <t>DIASEPTYL 0,5% SOL PULV 125ML</t>
         </is>
       </c>
-      <c r="C199" s="3" t="n">
+      <c r="H199" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I199" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J199" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
+          <t>2795647</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
           <t>3400927956478</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="inlineStr">
         <is>
           <t>DULCILARMES 1,5% COLLY DOS 60</t>
         </is>
       </c>
-      <c r="C200" s="3" t="n">
+      <c r="H200" s="3" t="n">
         <v>4.81</v>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I200" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J200" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
+          <t>3012144</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
           <t>3400930121443</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>INTEGRAL TOP 200</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="inlineStr">
         <is>
           <t>LEVOTHYROX 125MCG CPR BT90 EXC</t>
         </is>
       </c>
-      <c r="C201" s="3" t="n">
+      <c r="H201" s="3" t="n">
         <v>5.64</v>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>INTEGRAL TOP 200</t>
-        </is>
+      <c r="I201" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J201" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D201"/>
+  <autoFilter ref="A1:J201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>